--- a/examples/sequence/NORT/metadata.xlsx
+++ b/examples/sequence/NORT/metadata.xlsx
@@ -224,10 +224,10 @@
     <t xml:space="preserve">Trial_ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Perimeter left</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perimeter right</t>
+    <t xml:space="preserve">left object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">right object</t>
   </si>
   <si>
     <t xml:space="preserve">OO670_1</t>
@@ -647,7 +647,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="8.359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.3515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
   </cols>
@@ -1570,7 +1570,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultColWidth="8.359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.3515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.72"/>

--- a/examples/sequence/NORT/metadata.xlsx
+++ b/examples/sequence/NORT/metadata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="animal" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="perimeter_label" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -647,8 +647,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="8.3515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
   </cols>
   <sheetData>
@@ -1570,7 +1571,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultColWidth="8.3515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.72"/>

--- a/examples/sequence/NORT/metadata.xlsx
+++ b/examples/sequence/NORT/metadata.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="animal" sheetId="1" state="visible" r:id="rId2"/>
@@ -230,325 +230,325 @@
     <t xml:space="preserve">right object</t>
   </si>
   <si>
+    <t xml:space="preserve">OO670_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">variable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">familiar</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO670_1</t>
   </si>
   <si>
-    <t xml:space="preserve">variable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">familiar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OO670_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">novel</t>
   </si>
   <si>
+    <t xml:space="preserve">OO671_0</t>
+  </si>
+  <si>
     <t xml:space="preserve">OO671_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO671_2</t>
+    <t xml:space="preserve">OO672_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO672_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO672_2</t>
+    <t xml:space="preserve">OO685_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO685_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO685_2</t>
+    <t xml:space="preserve">OO686_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO686_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO686_2</t>
+    <t xml:space="preserve">OO687_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO687_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO687_2</t>
+    <t xml:space="preserve">OO725_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO725_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO725_2</t>
+    <t xml:space="preserve">OO728_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO728_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO728_2</t>
+    <t xml:space="preserve">OO731_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO731_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO731_2</t>
+    <t xml:space="preserve">OO735_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO735_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO735_2</t>
+    <t xml:space="preserve">OO736_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO736_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO736_2</t>
+    <t xml:space="preserve">OO737_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO737_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO737_2</t>
+    <t xml:space="preserve">OO738_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO738_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO738_2</t>
+    <t xml:space="preserve">OO743_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO743_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO743_2</t>
+    <t xml:space="preserve">OO745_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO745_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO745_2</t>
+    <t xml:space="preserve">OO941_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO941_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO941_2</t>
+    <t xml:space="preserve">OO942_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO942_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO942_2</t>
+    <t xml:space="preserve">OO943_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO943_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO943_2</t>
+    <t xml:space="preserve">OO944_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO944_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO944_2</t>
+    <t xml:space="preserve">OO945_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO945_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO945_2</t>
+    <t xml:space="preserve">OO953_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO953_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO953_2</t>
+    <t xml:space="preserve">OO954_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO954_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO954_2</t>
+    <t xml:space="preserve">OO955_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO955_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO955_2</t>
+    <t xml:space="preserve">OO956_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO956_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO956_2</t>
+    <t xml:space="preserve">OO957_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO957_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO957_2</t>
+    <t xml:space="preserve">OO958_0</t>
   </si>
   <si>
     <t xml:space="preserve">OO958_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OO958_2</t>
+    <t xml:space="preserve">OP210_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP210_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP210_2</t>
+    <t xml:space="preserve">OP211_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP211_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP211_2</t>
+    <t xml:space="preserve">OP212_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP212_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP212_2</t>
+    <t xml:space="preserve">OP213_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP213_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP213_2</t>
+    <t xml:space="preserve">OP214_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP214_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP214_2</t>
+    <t xml:space="preserve">OP215_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP215_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP215_2</t>
+    <t xml:space="preserve">OP216_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP216_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP216_2</t>
+    <t xml:space="preserve">OP220_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP220_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP220_2</t>
+    <t xml:space="preserve">OP222_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP222_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP222_2</t>
+    <t xml:space="preserve">OP224_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP224_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP224_2</t>
+    <t xml:space="preserve">OP337_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP337_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP337_2</t>
+    <t xml:space="preserve">OP338_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP338_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP338_2</t>
+    <t xml:space="preserve">OP339_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP339_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP339_2</t>
+    <t xml:space="preserve">OP351_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP351_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP351_2</t>
+    <t xml:space="preserve">OP352_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP352_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP352_2</t>
+    <t xml:space="preserve">OP353_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP353_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP353_2</t>
+    <t xml:space="preserve">OP679_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP679_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP679_2</t>
+    <t xml:space="preserve">OP680_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP680_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP680_2</t>
+    <t xml:space="preserve">OP689_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP689_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP689_2</t>
+    <t xml:space="preserve">OP691_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP691_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP691_2</t>
+    <t xml:space="preserve">OP696_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP696_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP696_2</t>
+    <t xml:space="preserve">OP697_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP697_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP697_2</t>
+    <t xml:space="preserve">OP698_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP698_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP698_2</t>
+    <t xml:space="preserve">OP700_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP700_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP700_2</t>
+    <t xml:space="preserve">OP721_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP721_1</t>
   </si>
   <si>
-    <t xml:space="preserve">OP721_2</t>
+    <t xml:space="preserve">OP722_0</t>
   </si>
   <si>
     <t xml:space="preserve">OP722_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OP722_2</t>
   </si>
 </sst>
 </file>
@@ -558,7 +558,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -581,6 +581,13 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -590,12 +597,19 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -624,9 +638,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -647,7 +665,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.3359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
@@ -1570,26 +1588,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
-  <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C105"/>
+  <sheetFormatPr defaultColWidth="8.3359375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.19"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B2" s="0" t="s">
@@ -1600,7 +1619,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
@@ -1611,7 +1630,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B4" s="0" t="s">
@@ -1622,7 +1641,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B5" s="0" t="s">
@@ -1633,7 +1652,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B6" s="0" t="s">
@@ -1644,7 +1663,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B7" s="0" t="s">
@@ -1655,7 +1674,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B8" s="0" t="s">
@@ -1666,7 +1685,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B9" s="0" t="s">
@@ -1677,7 +1696,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="0" t="s">
@@ -1688,7 +1707,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="0" t="s">
@@ -1699,7 +1718,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B12" s="0" t="s">
@@ -1710,7 +1729,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B13" s="0" t="s">
@@ -1721,7 +1740,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B14" s="0" t="s">
@@ -1732,7 +1751,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="0" t="s">
@@ -1743,7 +1762,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="0" t="s">
@@ -1754,7 +1773,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B17" s="0" t="s">
@@ -1765,7 +1784,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B18" s="0" t="s">
@@ -1776,7 +1795,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B19" s="0" t="s">
@@ -1787,7 +1806,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="0" t="s">
@@ -1798,7 +1817,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="0" t="s">
@@ -1809,7 +1828,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>92</v>
       </c>
       <c r="B22" s="0" t="s">
@@ -1820,7 +1839,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B23" s="0" t="s">
@@ -1831,7 +1850,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="0" t="s">
@@ -1842,7 +1861,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B25" s="0" t="s">
@@ -1853,7 +1872,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B26" s="0" t="s">
@@ -1864,7 +1883,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B27" s="0" t="s">
@@ -1875,7 +1894,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>98</v>
       </c>
       <c r="B28" s="0" t="s">
@@ -1886,7 +1905,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B29" s="0" t="s">
@@ -1897,7 +1916,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B30" s="0" t="s">
@@ -1908,7 +1927,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B31" s="0" t="s">
@@ -1919,7 +1938,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B32" s="0" t="s">
@@ -1930,7 +1949,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B33" s="0" t="s">
@@ -1941,7 +1960,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>104</v>
       </c>
       <c r="B34" s="0" t="s">
@@ -1952,7 +1971,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B35" s="0" t="s">
@@ -1963,7 +1982,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>106</v>
       </c>
       <c r="B36" s="0" t="s">
@@ -1974,7 +1993,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B37" s="0" t="s">
@@ -1985,7 +2004,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>108</v>
       </c>
       <c r="B38" s="0" t="s">
@@ -1996,7 +2015,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B39" s="0" t="s">
@@ -2007,7 +2026,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B40" s="0" t="s">
@@ -2018,7 +2037,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B41" s="0" t="s">
@@ -2029,7 +2048,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B42" s="0" t="s">
@@ -2040,7 +2059,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B43" s="0" t="s">
@@ -2051,7 +2070,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="1" t="s">
         <v>114</v>
       </c>
       <c r="B44" s="0" t="s">
@@ -2062,7 +2081,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B45" s="0" t="s">
@@ -2073,7 +2092,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="1" t="s">
         <v>116</v>
       </c>
       <c r="B46" s="0" t="s">
@@ -2084,7 +2103,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B47" s="0" t="s">
@@ -2095,7 +2114,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="1" t="s">
         <v>118</v>
       </c>
       <c r="B48" s="0" t="s">
@@ -2106,7 +2125,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B49" s="0" t="s">
@@ -2117,7 +2136,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="1" t="s">
         <v>120</v>
       </c>
       <c r="B50" s="0" t="s">
@@ -2128,7 +2147,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B51" s="0" t="s">
@@ -2139,7 +2158,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="1" t="s">
         <v>122</v>
       </c>
       <c r="B52" s="0" t="s">
@@ -2150,7 +2169,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B53" s="0" t="s">
@@ -2161,7 +2180,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
+      <c r="A54" s="1" t="s">
         <v>124</v>
       </c>
       <c r="B54" s="0" t="s">
@@ -2172,7 +2191,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
+      <c r="A55" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B55" s="0" t="s">
@@ -2183,7 +2202,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
+      <c r="A56" s="1" t="s">
         <v>126</v>
       </c>
       <c r="B56" s="0" t="s">
@@ -2194,7 +2213,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
+      <c r="A57" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B57" s="0" t="s">
@@ -2205,7 +2224,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
+      <c r="A58" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B58" s="0" t="s">
@@ -2216,7 +2235,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
+      <c r="A59" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B59" s="0" t="s">
@@ -2227,7 +2246,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+      <c r="A60" s="1" t="s">
         <v>130</v>
       </c>
       <c r="B60" s="0" t="s">
@@ -2238,7 +2257,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="A61" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B61" s="0" t="s">
@@ -2249,7 +2268,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="A62" s="1" t="s">
         <v>132</v>
       </c>
       <c r="B62" s="0" t="s">
@@ -2260,7 +2279,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="A63" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B63" s="0" t="s">
@@ -2271,7 +2290,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
+      <c r="A64" s="1" t="s">
         <v>134</v>
       </c>
       <c r="B64" s="0" t="s">
@@ -2282,7 +2301,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
+      <c r="A65" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B65" s="0" t="s">
@@ -2293,7 +2312,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
+      <c r="A66" s="1" t="s">
         <v>136</v>
       </c>
       <c r="B66" s="0" t="s">
@@ -2304,7 +2323,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
+      <c r="A67" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B67" s="0" t="s">
@@ -2315,7 +2334,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
+      <c r="A68" s="1" t="s">
         <v>138</v>
       </c>
       <c r="B68" s="0" t="s">
@@ -2326,7 +2345,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
+      <c r="A69" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B69" s="0" t="s">
@@ -2337,7 +2356,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
+      <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
       <c r="B70" s="0" t="s">
@@ -2348,7 +2367,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
+      <c r="A71" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B71" s="0" t="s">
@@ -2359,7 +2378,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="s">
+      <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
       <c r="B72" s="0" t="s">
@@ -2370,7 +2389,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="s">
+      <c r="A73" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B73" s="0" t="s">
@@ -2381,7 +2400,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="s">
+      <c r="A74" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B74" s="0" t="s">
@@ -2392,7 +2411,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
+      <c r="A75" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B75" s="0" t="s">
@@ -2403,7 +2422,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
+      <c r="A76" s="1" t="s">
         <v>146</v>
       </c>
       <c r="B76" s="0" t="s">
@@ -2414,7 +2433,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
+      <c r="A77" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B77" s="0" t="s">
@@ -2425,7 +2444,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
+      <c r="A78" s="1" t="s">
         <v>148</v>
       </c>
       <c r="B78" s="0" t="s">
@@ -2436,7 +2455,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
+      <c r="A79" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B79" s="0" t="s">
@@ -2447,7 +2466,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="s">
+      <c r="A80" s="1" t="s">
         <v>150</v>
       </c>
       <c r="B80" s="0" t="s">
@@ -2458,7 +2477,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="s">
+      <c r="A81" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B81" s="0" t="s">
@@ -2469,7 +2488,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+      <c r="A82" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B82" s="0" t="s">
@@ -2480,7 +2499,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
+      <c r="A83" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B83" s="0" t="s">
@@ -2491,7 +2510,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
+      <c r="A84" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B84" s="0" t="s">
@@ -2502,7 +2521,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="s">
+      <c r="A85" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B85" s="0" t="s">
@@ -2513,7 +2532,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="s">
+      <c r="A86" s="1" t="s">
         <v>156</v>
       </c>
       <c r="B86" s="0" t="s">
@@ -2524,7 +2543,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="s">
+      <c r="A87" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B87" s="0" t="s">
@@ -2535,7 +2554,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="s">
+      <c r="A88" s="1" t="s">
         <v>158</v>
       </c>
       <c r="B88" s="0" t="s">
@@ -2546,7 +2565,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="s">
+      <c r="A89" s="1" t="s">
         <v>159</v>
       </c>
       <c r="B89" s="0" t="s">
@@ -2557,7 +2576,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="s">
+      <c r="A90" s="1" t="s">
         <v>160</v>
       </c>
       <c r="B90" s="0" t="s">
@@ -2568,7 +2587,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="s">
+      <c r="A91" s="1" t="s">
         <v>161</v>
       </c>
       <c r="B91" s="0" t="s">
@@ -2579,7 +2598,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="s">
+      <c r="A92" s="1" t="s">
         <v>162</v>
       </c>
       <c r="B92" s="0" t="s">
@@ -2590,7 +2609,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="s">
+      <c r="A93" s="1" t="s">
         <v>163</v>
       </c>
       <c r="B93" s="0" t="s">
@@ -2601,7 +2620,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="s">
+      <c r="A94" s="1" t="s">
         <v>164</v>
       </c>
       <c r="B94" s="0" t="s">
@@ -2612,7 +2631,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="s">
+      <c r="A95" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B95" s="0" t="s">
@@ -2623,7 +2642,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="s">
+      <c r="A96" s="1" t="s">
         <v>166</v>
       </c>
       <c r="B96" s="0" t="s">
@@ -2634,7 +2653,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="s">
+      <c r="A97" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B97" s="0" t="s">
@@ -2645,7 +2664,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="s">
+      <c r="A98" s="1" t="s">
         <v>168</v>
       </c>
       <c r="B98" s="0" t="s">
@@ -2656,7 +2675,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="s">
+      <c r="A99" s="1" t="s">
         <v>169</v>
       </c>
       <c r="B99" s="0" t="s">
@@ -2667,7 +2686,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="s">
+      <c r="A100" s="1" t="s">
         <v>170</v>
       </c>
       <c r="B100" s="0" t="s">
@@ -2678,7 +2697,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="s">
+      <c r="A101" s="1" t="s">
         <v>171</v>
       </c>
       <c r="B101" s="0" t="s">
@@ -2689,7 +2708,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="s">
+      <c r="A102" s="1" t="s">
         <v>172</v>
       </c>
       <c r="B102" s="0" t="s">
@@ -2700,7 +2719,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="s">
+      <c r="A103" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B103" s="0" t="s">
@@ -2711,7 +2730,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="s">
+      <c r="A104" s="1" t="s">
         <v>174</v>
       </c>
       <c r="B104" s="0" t="s">
@@ -2722,7 +2741,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="s">
+      <c r="A105" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B105" s="0" t="s">
@@ -2732,7 +2751,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/examples/sequence/NORT/metadata.xlsx
+++ b/examples/sequence/NORT/metadata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="176">
   <si>
     <t xml:space="preserve">Animal</t>
   </si>
@@ -558,7 +558,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -580,6 +580,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -638,12 +646,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -665,911 +689,910 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E53"/>
-  <sheetFormatPr defaultColWidth="8.3359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.3515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="D4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>8</v>
+      <c r="D5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>685</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>8</v>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>686</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>8</v>
+      <c r="D7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>687</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="0" t="s">
-        <v>18</v>
+      <c r="E15" s="1" t="n">
+        <v>743</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>18</v>
+      <c r="E16" s="1" t="n">
+        <v>745</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="D21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>18</v>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>953</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>18</v>
+      <c r="D23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>954</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>18</v>
+      <c r="D24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>955</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>18</v>
+      <c r="D25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>956</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>18</v>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>957</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="0" t="s">
-        <v>18</v>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>958</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="0" t="s">
+      <c r="E35" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="0" t="s">
+      <c r="D38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="0" t="n">
+      <c r="C40" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C41" s="0" t="n">
+      <c r="C41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="0" t="s">
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="0" t="n">
+      <c r="C42" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="D42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="0" t="n">
+      <c r="C43" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="0" t="s">
+      <c r="D43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
+      <c r="A44" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="0" t="n">
+      <c r="C44" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="D44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
+      <c r="A45" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C45" s="0" t="n">
+      <c r="C45" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D45" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="0" t="s">
+      <c r="D45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
+      <c r="A46" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C46" s="0" t="n">
+      <c r="C46" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D46" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="0" t="s">
+      <c r="D46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
+      <c r="A47" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="0" t="n">
+      <c r="C47" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D47" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="0" t="s">
+      <c r="D47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
+      <c r="A48" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C48" s="0" t="n">
+      <c r="C48" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D48" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="0" t="s">
+      <c r="D48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
+      <c r="A49" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C49" s="0" t="n">
+      <c r="C49" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D49" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="0" t="s">
+      <c r="D49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
+      <c r="A50" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="0" t="n">
+      <c r="C50" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D50" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="0" t="s">
+      <c r="D50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
+      <c r="A51" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D51" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="0" t="s">
+      <c r="D51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
+      <c r="A52" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D52" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="0" t="s">
-        <v>18</v>
+      <c r="D52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>721</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
+      <c r="A53" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D53" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="0" t="s">
-        <v>18</v>
+      <c r="D53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -1589,1165 +1612,1165 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C105"/>
-  <sheetFormatPr defaultColWidth="8.3359375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.3515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.19"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="8.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.72"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="0" t="s">
+      <c r="B5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="B6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="B8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="0" t="s">
+      <c r="B9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="0" t="s">
+      <c r="B10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="0" t="s">
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="0" t="s">
+      <c r="B12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="0" t="s">
+      <c r="B13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" s="0" t="s">
+      <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="0" t="s">
+      <c r="B15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="0" t="s">
+      <c r="B16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="0" t="s">
+      <c r="B17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B18" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C18" s="0" t="s">
+      <c r="B18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B19" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="0" t="s">
+      <c r="B19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="0" t="s">
+      <c r="B20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="0" t="s">
+      <c r="B21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="0" t="s">
+      <c r="B22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" s="0" t="s">
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="0" t="s">
+      <c r="B24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="0" t="s">
+      <c r="B25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B26" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="0" t="s">
+      <c r="B26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="0" t="s">
+      <c r="B27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B28" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="0" t="s">
+      <c r="B28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="0" t="s">
+      <c r="B29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B30" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="0" t="s">
+      <c r="B30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="0" t="s">
+      <c r="B31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B32" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="0" t="s">
+      <c r="B32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B33" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="0" t="s">
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="0" t="s">
+      <c r="B34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B35" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="0" t="s">
+      <c r="B35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="0" t="s">
+      <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" s="0" t="s">
+      <c r="B37" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="0" t="s">
+      <c r="B38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="0" t="s">
+      <c r="B39" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B40" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="0" t="s">
+      <c r="B40" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="B41" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C41" s="0" t="s">
+      <c r="B41" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C42" s="0" t="s">
+      <c r="B42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C43" s="0" t="s">
+      <c r="B43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="0" t="s">
+      <c r="B44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B45" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C45" s="0" t="s">
+      <c r="B45" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B46" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="0" t="s">
+      <c r="B46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B47" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="0" t="s">
+      <c r="B47" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B48" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="0" t="s">
+      <c r="B48" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B49" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="0" t="s">
+      <c r="B49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B50" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="0" t="s">
+      <c r="B50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B51" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="0" t="s">
+      <c r="B51" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="0" t="s">
+      <c r="B52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B53" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="0" t="s">
+      <c r="B53" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" s="0" t="s">
+      <c r="B54" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C55" s="0" t="s">
+      <c r="B55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B56" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C56" s="0" t="s">
+      <c r="B56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C57" s="0" t="s">
+      <c r="B57" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="0" t="s">
+      <c r="B58" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C59" s="0" t="s">
+      <c r="B59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B60" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C60" s="0" t="s">
+      <c r="B60" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B61" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" s="0" t="s">
+      <c r="B61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B62" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C62" s="0" t="s">
+      <c r="B62" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" s="0" t="s">
+      <c r="B63" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C64" s="0" t="s">
+      <c r="B64" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B65" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C65" s="0" t="s">
+      <c r="B65" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B66" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C66" s="0" t="s">
+      <c r="B66" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B67" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C67" s="0" t="s">
+      <c r="B67" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B68" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" s="0" t="s">
+      <c r="B68" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B69" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C69" s="0" t="s">
+      <c r="B69" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="0" t="s">
+      <c r="B70" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B71" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C71" s="0" t="s">
+      <c r="B71" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" s="0" t="s">
+      <c r="B72" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="B73" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C73" s="0" t="s">
+      <c r="B73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B74" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C74" s="0" t="s">
+      <c r="B74" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B75" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C75" s="0" t="s">
+      <c r="B75" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="B76" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C76" s="0" t="s">
+      <c r="B76" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B77" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C77" s="0" t="s">
+      <c r="B77" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B78" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C78" s="0" t="s">
+      <c r="B78" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="B79" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C79" s="0" t="s">
+      <c r="B79" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B80" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C80" s="0" t="s">
+      <c r="B80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B81" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C81" s="0" t="s">
+      <c r="B81" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B82" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C82" s="0" t="s">
+      <c r="B82" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B83" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C83" s="0" t="s">
+      <c r="B83" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="B84" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="C84" s="0" t="s">
+      <c r="B84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B85" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C85" s="0" t="s">
+      <c r="B85" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B86" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C86" s="0" t="s">
+      <c r="B86" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B87" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C87" s="0" t="s">
+      <c r="B87" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="B88" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C88" s="0" t="s">
+      <c r="B88" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B89" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C89" s="0" t="s">
+      <c r="B89" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="B90" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C90" s="0" t="s">
+      <c r="B90" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B91" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C91" s="0" t="s">
+      <c r="B91" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B92" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C92" s="0" t="s">
+      <c r="B92" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B93" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C93" s="0" t="s">
+      <c r="B93" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="B94" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C94" s="0" t="s">
+      <c r="B94" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B95" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C95" s="0" t="s">
+      <c r="B95" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B96" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C96" s="0" t="s">
+      <c r="B96" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B97" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C97" s="0" t="s">
+      <c r="B97" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B98" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C98" s="0" t="s">
+      <c r="B98" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B99" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C99" s="0" t="s">
+      <c r="B99" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B100" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C100" s="0" t="s">
+      <c r="B100" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B101" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C101" s="0" t="s">
+      <c r="B101" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B102" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C102" s="0" t="s">
+      <c r="B102" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B103" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C103" s="0" t="s">
+      <c r="B103" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B104" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C104" s="0" t="s">
+      <c r="B104" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B105" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C105" s="0" t="s">
+      <c r="B105" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>73</v>
       </c>
     </row>
